--- a/Class-7, Student Data-Main File-2026/Class-7, E.xlsx
+++ b/Class-7, Student Data-Main File-2026/Class-7, E.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WLP Document\Student Data-Main File-2026\Class-7, Student Data-Main File-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38255414-70F5-474A-8147-BA258F15798A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CEE446B-4B1E-4210-A60B-F016807DEF4A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8736" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1747,7 +1747,7 @@
         <v>45</v>
       </c>
       <c r="D23" s="5">
-        <v>1759653159</v>
+        <v>1779783215</v>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
